--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1965229</v>
+        <v>871842</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627904.2394050588</v>
+        <v>627904</v>
       </c>
       <c r="R2" t="n">
-        <v>7115227.847999226</v>
+        <v>7115228</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2010-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1936924</v>
+        <v>1843272</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627904.2394050588</v>
+        <v>627924</v>
       </c>
       <c r="R3" t="n">
-        <v>7115227.847999226</v>
+        <v>7115019</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på gran och lodyta</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1843272</v>
+        <v>1844549</v>
       </c>
       <c r="B4" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,13 +909,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627923.8159934728</v>
+        <v>628253</v>
       </c>
       <c r="R4" t="n">
-        <v>7115018.846562805</v>
+        <v>7114837</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +939,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gran och lodyta</t>
+          <t>med appotecier</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>871842</v>
+        <v>1965229</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627904.2394050588</v>
+        <v>627904</v>
       </c>
       <c r="R5" t="n">
-        <v>7115227.847999226</v>
+        <v>7115228</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1044,9 @@
           <t>2010-09-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1967280</v>
+        <v>1967279</v>
       </c>
       <c r="B6" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628222.2918520449</v>
+        <v>628172</v>
       </c>
       <c r="R6" t="n">
-        <v>7114839.727877217</v>
+        <v>7114987</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1141,9 @@
           <t>2010-10-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1967283</v>
+        <v>1967280</v>
       </c>
       <c r="B7" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628232.0856954739</v>
+        <v>628222</v>
       </c>
       <c r="R7" t="n">
-        <v>7114835.761968906</v>
+        <v>7114840</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1313,19 +1238,9 @@
           <t>2010-10-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1844549</v>
+        <v>1967281</v>
       </c>
       <c r="B8" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628253.0417167862</v>
+        <v>628227</v>
       </c>
       <c r="R8" t="n">
-        <v>7114837.067046419</v>
+        <v>7114887</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1425,24 +1335,9 @@
           <t>2010-10-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>med appotecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1967281</v>
+        <v>1967283</v>
       </c>
       <c r="B9" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628227.3494747295</v>
+        <v>628232</v>
       </c>
       <c r="R9" t="n">
-        <v>7114886.711857916</v>
+        <v>7114836</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,19 +1432,9 @@
           <t>2010-10-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1937621</v>
+        <v>2064226</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628172.4176609679</v>
+        <v>628220</v>
       </c>
       <c r="R10" t="n">
-        <v>7114987.164050519</v>
+        <v>7114879</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1654,19 +1529,9 @@
           <t>2010-10-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2064226</v>
+        <v>1936924</v>
       </c>
       <c r="B11" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628219.7915252086</v>
+        <v>627904</v>
       </c>
       <c r="R11" t="n">
-        <v>7114878.967451937</v>
+        <v>7115228</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,22 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1967279</v>
+        <v>1937621</v>
       </c>
       <c r="B12" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628172.4176609679</v>
+        <v>628172</v>
       </c>
       <c r="R12" t="n">
-        <v>7114987.164050519</v>
+        <v>7114987</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1878,19 +1723,9 @@
           <t>2010-10-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1843272</v>
+        <v>135444691</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>96413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627924</v>
+        <v>627855</v>
       </c>
       <c r="R3" t="n">
-        <v>7115019</v>
+        <v>7115126</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,17 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på gran och lodyta</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,44 +867,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1965229</v>
+        <v>1843272</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627904</v>
+        <v>627924</v>
       </c>
       <c r="R4" t="n">
-        <v>7115228</v>
+        <v>7115019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,12 +948,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2010-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2010-09-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på gran och lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,27 +985,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1936924</v>
+        <v>135444657</v>
       </c>
       <c r="B5" t="n">
-        <v>80467</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1002,17 +1016,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627904</v>
+        <v>627807</v>
       </c>
       <c r="R5" t="n">
-        <v>7115228</v>
+        <v>7115167</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1050,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1056,22 +1080,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1844549</v>
+        <v>135444663</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,17 +1127,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628253</v>
+        <v>627917</v>
       </c>
       <c r="R6" t="n">
-        <v>7114837</v>
+        <v>7114978</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,17 +1161,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>med appotecier</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1158,60 +1191,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1967279</v>
+        <v>135444690</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628172</v>
+        <v>627955</v>
       </c>
       <c r="R7" t="n">
-        <v>7114987</v>
+        <v>7115004</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1235,12 +1272,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1255,19 +1302,23 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1967280</v>
+        <v>1965229</v>
       </c>
       <c r="B8" t="n">
         <v>80432</v>
@@ -1302,13 +1353,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628222</v>
+        <v>627904</v>
       </c>
       <c r="R8" t="n">
-        <v>7114840</v>
+        <v>7115228</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1332,12 +1383,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1967281</v>
+        <v>135444689</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,17 +1446,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628227</v>
+        <v>627980</v>
       </c>
       <c r="R9" t="n">
-        <v>7114887</v>
+        <v>7114997</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1429,12 +1480,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1449,44 +1510,48 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1967283</v>
+        <v>1936924</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1561,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628232</v>
+        <v>627904</v>
       </c>
       <c r="R10" t="n">
-        <v>7114836</v>
+        <v>7115228</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1526,12 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2064226</v>
+        <v>135444658</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80500</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,37 +1634,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628220</v>
+        <v>627832</v>
       </c>
       <c r="R11" t="n">
-        <v>7114879</v>
+        <v>7115096</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1623,12 +1688,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1643,22 +1718,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1937621</v>
+        <v>135444662</v>
       </c>
       <c r="B12" t="n">
-        <v>80467</v>
+        <v>80500</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,37 +1745,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628172</v>
+        <v>627856</v>
       </c>
       <c r="R12" t="n">
-        <v>7114987</v>
+        <v>7115008</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1720,12 +1799,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1740,15 +1829,2277 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135444664</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627927</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7114947</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135444659</v>
+      </c>
+      <c r="B14" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627829</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7115057</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135444656</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627764</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7115212</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135444661</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>627853</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7115004</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135444676</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>628183</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7114781</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1844549</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>628253</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7114837</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>med appotecier</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Karin Häggblad</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Karin Häggblad</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135444679</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628192</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7114799</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1967279</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628172</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7114987</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1967280</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>628222</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7114840</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1967281</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628227</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7114887</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1967283</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628232</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7114836</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2064226</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>628220</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7114879</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1937621</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>628172</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7114987</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135444682</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80500</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>628180</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7114827</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135444674</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628170</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7114761</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135444687</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>627997</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7114983</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135444675</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>628182</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7114779</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135444681</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>628179</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7114818</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135444685</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>628007</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7114984</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135444688</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>627990</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7114988</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135444680</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>628184</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7114810</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/871842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1843272</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444657</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444663</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444690</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1965229</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444689</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1936924</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444658</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444662</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2069,6 +2134,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444659</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444656</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444661</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2402,6 +2482,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444676</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1844549</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444679</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967279</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2809,6 +2909,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967280</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2906,6 +3011,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967281</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3003,6 +3113,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967283</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3100,6 +3215,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2064226</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3197,6 +3317,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937621</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3308,6 +3433,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444682</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3424,6 +3554,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444674</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444687</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3656,6 +3796,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444675</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3767,6 +3912,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444681</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3878,6 +4028,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444685</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444688</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4100,8 +4260,47 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135444691</v>
       </c>
       <c r="B3" t="n">
-        <v>96413</v>
+        <v>96457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135444657</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135444663</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>135444690</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135444689</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135444658</v>
       </c>
       <c r="B11" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>135444662</v>
       </c>
       <c r="B12" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135444664</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>135444659</v>
       </c>
       <c r="B14" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135444656</v>
       </c>
       <c r="B15" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135444661</v>
       </c>
       <c r="B16" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135444676</v>
       </c>
       <c r="B17" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>135444679</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>135444682</v>
       </c>
       <c r="B26" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135444674</v>
       </c>
       <c r="B27" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135444687</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>135444675</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>135444681</v>
       </c>
       <c r="B30" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135444685</v>
       </c>
       <c r="B31" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135444688</v>
       </c>
       <c r="B32" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135444680</v>
       </c>
       <c r="B33" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135444691</v>
       </c>
       <c r="B3" t="n">
-        <v>96457</v>
+        <v>96484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135444657</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135444663</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>135444690</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135444689</v>
       </c>
       <c r="B9" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135444658</v>
       </c>
       <c r="B11" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>135444662</v>
       </c>
       <c r="B12" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>135444659</v>
       </c>
       <c r="B14" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135444656</v>
       </c>
       <c r="B15" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135444661</v>
       </c>
       <c r="B16" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135444676</v>
       </c>
       <c r="B17" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>135444679</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>135444682</v>
       </c>
       <c r="B26" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>135444681</v>
       </c>
       <c r="B30" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135444685</v>
       </c>
       <c r="B31" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135444688</v>
       </c>
       <c r="B32" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135444680</v>
       </c>
       <c r="B33" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1843272</v>
+        <v>135444691</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>96489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627924</v>
+        <v>627855</v>
       </c>
       <c r="R3" t="n">
-        <v>7115019</v>
+        <v>7115126</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på gran och lodyta</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,49 +877,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1843272</t>
+          <t>https://artportalen.se/Sighting/135444691</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1965229</v>
+        <v>1843272</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627904</v>
+        <v>627924</v>
       </c>
       <c r="R4" t="n">
-        <v>7115228</v>
+        <v>7115019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2010-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2010-09-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på gran och lodyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,33 +999,33 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1965229</t>
+          <t>https://artportalen.se/Sighting/1843272</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1936924</v>
+        <v>135444657</v>
       </c>
       <c r="B5" t="n">
-        <v>80467</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1022,17 +1036,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627904</v>
+        <v>627807</v>
       </c>
       <c r="R5" t="n">
-        <v>7115228</v>
+        <v>7115167</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1070,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-09-13</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,27 +1100,31 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1936924</t>
+          <t>https://artportalen.se/Sighting/135444657</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1844549</v>
+        <v>135444663</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>79441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,17 +1152,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628253</v>
+        <v>627917</v>
       </c>
       <c r="R6" t="n">
-        <v>7114837</v>
+        <v>7114978</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,17 +1186,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>med appotecier</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,65 +1216,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1844549</t>
+          <t>https://artportalen.se/Sighting/135444663</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1967279</v>
+        <v>135444690</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628172</v>
+        <v>627955</v>
       </c>
       <c r="R7" t="n">
-        <v>7114987</v>
+        <v>7115004</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1265,12 +1302,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,24 +1332,28 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1967279</t>
+          <t>https://artportalen.se/Sighting/135444690</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1967280</v>
+        <v>1965229</v>
       </c>
       <c r="B8" t="n">
         <v>80432</v>
@@ -1337,13 +1388,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628222</v>
+        <v>627904</v>
       </c>
       <c r="R8" t="n">
-        <v>7114840</v>
+        <v>7115228</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1367,12 +1418,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,16 +1449,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1967280</t>
+          <t>https://artportalen.se/Sighting/1965229</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1967281</v>
+        <v>135444689</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>80556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,17 +1486,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628227</v>
+        <v>627980</v>
       </c>
       <c r="R9" t="n">
-        <v>7114887</v>
+        <v>7114997</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1469,12 +1520,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,49 +1550,53 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1967281</t>
+          <t>https://artportalen.se/Sighting/135444689</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1967283</v>
+        <v>1936924</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>80467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1606,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628232</v>
+        <v>627904</v>
       </c>
       <c r="R10" t="n">
-        <v>7114836</v>
+        <v>7115228</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1571,12 +1636,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2010-09-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,16 +1667,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1967283</t>
+          <t>https://artportalen.se/Sighting/1936924</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2064226</v>
+        <v>135444658</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,37 +1684,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628220</v>
+        <v>627832</v>
       </c>
       <c r="R11" t="n">
-        <v>7114879</v>
+        <v>7115096</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1673,12 +1738,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,27 +1768,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karin Häggblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2064226</t>
+          <t>https://artportalen.se/Sighting/135444658</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1937621</v>
+        <v>135444662</v>
       </c>
       <c r="B12" t="n">
-        <v>80467</v>
+        <v>80568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,37 +1800,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storsjöliden, Ås lm</t>
+          <t>Storsjöliden, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628172</v>
+        <v>627856</v>
       </c>
       <c r="R12" t="n">
-        <v>7114987</v>
+        <v>7115008</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1775,12 +1854,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-10-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,18 +1884,2385 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444662</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135444664</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627927</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7114947</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444664</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135444659</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110012</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627829</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7115057</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444659</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135444656</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627764</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7115212</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444656</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135444661</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>627853</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7115004</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444661</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135444676</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>628183</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7114781</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444676</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1844549</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>628253</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7114837</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>med appotecier</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Karin Häggblad</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Karin Häggblad</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1844549</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135444679</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628192</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7114799</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444679</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1967279</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628172</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7114987</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967279</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1967280</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>628222</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7114840</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967280</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1967281</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628227</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7114887</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967281</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1967283</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>628232</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7114836</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1967283</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2064226</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>628220</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7114879</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2064226</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1937621</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>628172</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7114987</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2010-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karin Häggblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1937621</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135444682</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>628180</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7114827</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444682</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135444674</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>628170</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7114761</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444674</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135444687</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>627997</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7114983</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444687</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135444675</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>628182</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7114779</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444675</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135444681</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>628179</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7114818</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444681</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135444685</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>628007</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7114984</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444685</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135444688</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99191</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>627990</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7114988</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444688</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135444680</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storsjöliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>628184</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7114810</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444680</t>
         </is>
       </c>
     </row>
@@ -1823,6 +4279,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135444691</v>
       </c>
       <c r="B3" t="n">
-        <v>96489</v>
+        <v>96491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>135444659</v>
       </c>
       <c r="B14" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135444656</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135444661</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135444676</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>135444681</v>
       </c>
       <c r="B30" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135444685</v>
       </c>
       <c r="B31" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135444688</v>
       </c>
       <c r="B32" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135444680</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 8655-2024 artfynd.xlsx
+++ b/artfynd/A 8655-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135444691</v>
       </c>
       <c r="B3" t="n">
-        <v>96491</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>135444657</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135444663</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>135444690</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>135444689</v>
       </c>
       <c r="B9" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>135444658</v>
       </c>
       <c r="B11" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>135444662</v>
       </c>
       <c r="B12" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>135444664</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>135444659</v>
       </c>
       <c r="B14" t="n">
-        <v>110014</v>
+        <v>110037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135444656</v>
       </c>
       <c r="B15" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135444661</v>
       </c>
       <c r="B16" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>135444676</v>
       </c>
       <c r="B17" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>135444679</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>135444682</v>
       </c>
       <c r="B26" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>135444674</v>
       </c>
       <c r="B27" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135444687</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>135444675</v>
       </c>
       <c r="B29" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>135444681</v>
       </c>
       <c r="B30" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135444685</v>
       </c>
       <c r="B31" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135444688</v>
       </c>
       <c r="B32" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135444680</v>
       </c>
       <c r="B33" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
